--- a/LakeAnalyzer/sp.metab.ols.inst.xlsx
+++ b/LakeAnalyzer/sp.metab.ols.inst.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayersj\R\WaterQuality\LakeAnalyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAD7A7D-4DF9-434F-A2A8-2124946F57F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3063EF45-DED4-42AA-8E39-5FA81DC58885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C94288ED-E09B-41F1-8AE2-8AB87FD8A12B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="66" r:id="rId2"/>
+    <pivotCache cacheId="67" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
@@ -691,7 +691,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -704,7 +704,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -8793,12 +8792,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -12130,7 +12124,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{423ECB36-09C2-423D-A4AE-74B493E2689C}" name="PivotTable2" cacheId="66" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{423ECB36-09C2-423D-A4AE-74B493E2689C}" name="PivotTable2" cacheId="67" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H20:I30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -14502,10 +14496,10 @@
         <v>31</v>
       </c>
       <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" t="s">
         <v>29</v>
-      </c>
-      <c r="K20" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -14532,15 +14526,15 @@
       <c r="H21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21">
         <v>9.936436149546525E-2</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21">
+        <v>4.4979435132249099E-2</v>
+      </c>
+      <c r="K21" s="2">
         <f>SUM(C2:C144)</f>
         <v>9.9358797744340963E-2</v>
-      </c>
-      <c r="K21">
-        <v>4.4979435132249099E-2</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -14567,15 +14561,15 @@
       <c r="H22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22">
         <v>0.19716449499653019</v>
       </c>
       <c r="J22">
+        <v>1.67514260855074E-2</v>
+      </c>
+      <c r="K22">
         <f>SUM(C145:C288)</f>
         <v>0.19715808899014434</v>
-      </c>
-      <c r="K22">
-        <v>1.67514260855074E-2</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -14602,15 +14596,15 @@
       <c r="H23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23">
         <v>0.22735117625361256</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23">
+        <v>0.347699404969255</v>
+      </c>
+      <c r="K23" s="2">
         <f>SUM(C289:C432)</f>
         <v>0.22734342057396123</v>
-      </c>
-      <c r="K23">
-        <v>0.347699404969255</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -14637,10 +14631,10 @@
       <c r="H24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24">
         <v>0.22724880712915649</v>
       </c>
-      <c r="K24">
+      <c r="J24">
         <v>0.39001682989476499</v>
       </c>
     </row>
@@ -14668,10 +14662,10 @@
       <c r="H25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25">
         <v>0.25648916265449634</v>
       </c>
-      <c r="K25">
+      <c r="J25">
         <v>0.35635889188176201</v>
       </c>
     </row>
@@ -14699,10 +14693,10 @@
       <c r="H26" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26">
         <v>0.2437364696441032</v>
       </c>
-      <c r="K26">
+      <c r="J26">
         <v>0.65564083754772395</v>
       </c>
     </row>
@@ -14730,10 +14724,10 @@
       <c r="H27" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27">
         <v>0.25030845588056139</v>
       </c>
-      <c r="K27">
+      <c r="J27">
         <v>-0.20160699337883101</v>
       </c>
     </row>
@@ -14761,10 +14755,10 @@
       <c r="H28" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28">
         <v>0.24266444953894081</v>
       </c>
-      <c r="K28">
+      <c r="J28">
         <v>0.24395999008063601</v>
       </c>
     </row>
@@ -14792,10 +14786,10 @@
       <c r="H29" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29">
         <v>0.20491540723766788</v>
       </c>
-      <c r="K29">
+      <c r="J29">
         <v>4.00527487791126E-2</v>
       </c>
     </row>
@@ -14823,7 +14817,7 @@
       <c r="H30" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30">
         <v>1.9492427848305336</v>
       </c>
     </row>
